--- a/App_Investimentos.xlsx
+++ b/App_Investimentos.xlsx
@@ -5,26 +5,26 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\apsou\OneDrive\Área de Trabalho\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/217cc67307c45ea1/Área de Trabalho/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA77CDAA-366C-4305-9366-5619397C2ED5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="93" documentId="13_ncr:1_{AA77CDAA-366C-4305-9366-5619397C2ED5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8142D5CE-75E9-406F-8756-0A29E0C3EAE5}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" xr2:uid="{5D7F3A9A-47AD-4D1B-B95A-5B68640EB23A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" tabRatio="0" xr2:uid="{5D7F3A9A-47AD-4D1B-B95A-5B68640EB23A}"/>
   </bookViews>
   <sheets>
     <sheet name="App" sheetId="1" r:id="rId1"/>
     <sheet name="Auxiliar" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="Aporte">App!$D$13</definedName>
-    <definedName name="Patrimonio">App!$D$16</definedName>
-    <definedName name="Percentual">App!$D$9</definedName>
-    <definedName name="Qtde_Anos">App!$D$14</definedName>
-    <definedName name="Rendimento">App!$D$8</definedName>
-    <definedName name="Salario">App!$D$7</definedName>
-    <definedName name="Taxa_Mensal">App!$D$15</definedName>
-    <definedName name="Valor">App!$D$10</definedName>
+    <definedName name="Aporte">App!$D$12</definedName>
+    <definedName name="Patrimonio">App!$D$15</definedName>
+    <definedName name="Percentual">App!$D$8</definedName>
+    <definedName name="Qtde_Anos">App!$D$13</definedName>
+    <definedName name="Rendimento">App!$D$7</definedName>
+    <definedName name="Salario">App!$D$6</definedName>
+    <definedName name="Taxa_Mensal">App!$D$14</definedName>
+    <definedName name="Valor">App!$D$9</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -61,9 +61,6 @@
     <t>Valor a ser investido (R$)</t>
   </si>
   <si>
-    <t>Aporte Mensal</t>
-  </si>
-  <si>
     <t>Percentual investido (%)</t>
   </si>
   <si>
@@ -211,7 +208,10 @@
     <t>Totalizador</t>
   </si>
   <si>
-    <t>Tipo de Fundo</t>
+    <t>Tipo de fundo</t>
+  </si>
+  <si>
+    <t>Aporte</t>
   </si>
 </sst>
 </file>
@@ -222,7 +222,7 @@
     <numFmt numFmtId="44" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="_-[$R$-416]\ * #,##0.00_-;\-[$R$-416]\ * #,##0.00_-;_-[$R$-416]\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -238,69 +238,32 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color theme="0"/>
-      <name val="Cooper Black"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Neue Haas Grotesk Text Pro"/>
       <family val="2"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Neue Haas Grotesk Text Pro"/>
+      <sz val="14"/>
+      <color theme="0"/>
+      <name val="Century Gothic"/>
       <family val="2"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Neue Haas Grotesk Text Pro"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="0"/>
-      <name val="Neue Haas Grotesk Text Pro"/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Century Gothic"/>
       <family val="2"/>
     </font>
     <font>
       <i/>
-      <sz val="12"/>
+      <sz val="14"/>
       <color theme="1"/>
-      <name val="Neue Haas Grotesk Text Pro"/>
+      <name val="Century Gothic"/>
       <family val="2"/>
     </font>
-    <font>
-      <i/>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="16"/>
-      <color theme="1"/>
-      <name val="Baguet Script"/>
-    </font>
-    <font>
-      <sz val="16"/>
-      <color theme="0"/>
-      <name val="Baguet Script"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -311,6 +274,12 @@
       <patternFill patternType="solid">
         <fgColor theme="1"/>
         <bgColor theme="1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -414,109 +383,107 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="4" fillId="0" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="2" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="4" fillId="0" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="3" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="3" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="8" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="5" fillId="0" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="5" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="5" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="5" fillId="0" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="11" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -635,10 +602,10 @@
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
+      <c14:style val="101"/>
     </mc:Choice>
     <mc:Fallback>
-      <c:style val="2"/>
+      <c:style val="1"/>
     </mc:Fallback>
   </mc:AlternateContent>
   <c:chart>
@@ -652,7 +619,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>App!$C$29</c:f>
+              <c:f>App!$C$28</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -668,13 +635,16 @@
               <a:gradFill>
                 <a:gsLst>
                   <a:gs pos="100000">
-                    <a:schemeClr val="accent1">
+                    <a:schemeClr val="dk1">
+                      <a:tint val="88500"/>
                       <a:lumMod val="60000"/>
                       <a:lumOff val="40000"/>
                     </a:schemeClr>
                   </a:gs>
                   <a:gs pos="0">
-                    <a:schemeClr val="accent1"/>
+                    <a:schemeClr val="dk1">
+                      <a:tint val="88500"/>
+                    </a:schemeClr>
                   </a:gs>
                 </a:gsLst>
                 <a:lin ang="5400000" scaled="0"/>
@@ -686,6 +656,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-4E94-49A4-A05F-F90E87FD74AA}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="1"/>
@@ -694,13 +669,16 @@
               <a:gradFill>
                 <a:gsLst>
                   <a:gs pos="100000">
-                    <a:schemeClr val="accent2">
+                    <a:schemeClr val="dk1">
+                      <a:tint val="55000"/>
                       <a:lumMod val="60000"/>
                       <a:lumOff val="40000"/>
                     </a:schemeClr>
                   </a:gs>
                   <a:gs pos="0">
-                    <a:schemeClr val="accent2"/>
+                    <a:schemeClr val="dk1">
+                      <a:tint val="55000"/>
+                    </a:schemeClr>
                   </a:gs>
                 </a:gsLst>
                 <a:lin ang="5400000" scaled="0"/>
@@ -712,6 +690,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-4E94-49A4-A05F-F90E87FD74AA}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="2"/>
@@ -720,13 +703,16 @@
               <a:gradFill>
                 <a:gsLst>
                   <a:gs pos="100000">
-                    <a:schemeClr val="accent3">
+                    <a:schemeClr val="dk1">
+                      <a:tint val="75000"/>
                       <a:lumMod val="60000"/>
                       <a:lumOff val="40000"/>
                     </a:schemeClr>
                   </a:gs>
                   <a:gs pos="0">
-                    <a:schemeClr val="accent3"/>
+                    <a:schemeClr val="dk1">
+                      <a:tint val="75000"/>
+                    </a:schemeClr>
                   </a:gs>
                 </a:gsLst>
                 <a:lin ang="5400000" scaled="0"/>
@@ -738,6 +724,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000005-4E94-49A4-A05F-F90E87FD74AA}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="3"/>
@@ -746,13 +737,16 @@
               <a:gradFill>
                 <a:gsLst>
                   <a:gs pos="100000">
-                    <a:schemeClr val="accent4">
+                    <a:schemeClr val="dk1">
+                      <a:tint val="98500"/>
                       <a:lumMod val="60000"/>
                       <a:lumOff val="40000"/>
                     </a:schemeClr>
                   </a:gs>
                   <a:gs pos="0">
-                    <a:schemeClr val="accent4"/>
+                    <a:schemeClr val="dk1">
+                      <a:tint val="98500"/>
+                    </a:schemeClr>
                   </a:gs>
                 </a:gsLst>
                 <a:lin ang="5400000" scaled="0"/>
@@ -764,6 +758,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000007-4E94-49A4-A05F-F90E87FD74AA}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="4"/>
@@ -772,13 +771,16 @@
               <a:gradFill>
                 <a:gsLst>
                   <a:gs pos="100000">
-                    <a:schemeClr val="accent5">
+                    <a:schemeClr val="dk1">
+                      <a:tint val="30000"/>
                       <a:lumMod val="60000"/>
                       <a:lumOff val="40000"/>
                     </a:schemeClr>
                   </a:gs>
                   <a:gs pos="0">
-                    <a:schemeClr val="accent5"/>
+                    <a:schemeClr val="dk1">
+                      <a:tint val="30000"/>
+                    </a:schemeClr>
                   </a:gs>
                 </a:gsLst>
                 <a:lin ang="5400000" scaled="0"/>
@@ -790,6 +792,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000009-4E94-49A4-A05F-F90E87FD74AA}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="5"/>
@@ -798,13 +805,16 @@
               <a:gradFill>
                 <a:gsLst>
                   <a:gs pos="100000">
-                    <a:schemeClr val="accent6">
+                    <a:schemeClr val="dk1">
+                      <a:tint val="60000"/>
                       <a:lumMod val="60000"/>
                       <a:lumOff val="40000"/>
                     </a:schemeClr>
                   </a:gs>
                   <a:gs pos="0">
-                    <a:schemeClr val="accent6"/>
+                    <a:schemeClr val="dk1">
+                      <a:tint val="60000"/>
+                    </a:schemeClr>
                   </a:gs>
                 </a:gsLst>
                 <a:lin ang="5400000" scaled="0"/>
@@ -816,6 +826,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000000B-4E94-49A4-A05F-F90E87FD74AA}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dLbls>
             <c:spPr>
@@ -832,11 +847,11 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr sz="1200" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
                       <a:sysClr val="windowText" lastClr="000000"/>
                     </a:solidFill>
-                    <a:latin typeface="Neue Haas Grotesk Text Pro" panose="020B0504020202020204" pitchFamily="34" charset="0"/>
+                    <a:latin typeface="Century Gothic" panose="020B0502020202020204" pitchFamily="34" charset="0"/>
                     <a:ea typeface="+mn-ea"/>
                     <a:cs typeface="+mn-cs"/>
                   </a:defRPr>
@@ -872,7 +887,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>App!$B$30:$B$35</c:f>
+              <c:f>App!$B$29:$B$34</c:f>
               <c:strCache>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
@@ -898,27 +913,27 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>App!$C$30:$C$35</c:f>
+              <c:f>App!$C$29:$C$34</c:f>
               <c:numCache>
                 <c:formatCode>0.00%</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
+                  <c:v>0.3</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>0.5</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="2">
                   <c:v>0.1</c:v>
                 </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.05</c:v>
-                </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.05</c:v>
+                  <c:v>0.1</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.2</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -968,14 +983,14 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="900" b="0" i="1" u="none" strike="noStrike" kern="1200" baseline="0">
+            <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
                 <a:schemeClr val="dk1">
                   <a:lumMod val="65000"/>
                   <a:lumOff val="35000"/>
                 </a:schemeClr>
               </a:solidFill>
-              <a:latin typeface="Neue Haas Grotesk Text Pro" panose="020B0504020202020204" pitchFamily="34" charset="0"/>
+              <a:latin typeface="Century Gothic" panose="020B0502020202020204" pitchFamily="34" charset="0"/>
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
@@ -1015,41 +1030,28 @@
 </file>
 
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
-  <a:schemeClr val="accent1"/>
-  <a:schemeClr val="accent2"/>
-  <a:schemeClr val="accent3"/>
-  <a:schemeClr val="accent4"/>
-  <a:schemeClr val="accent5"/>
-  <a:schemeClr val="accent6"/>
-  <cs:variation/>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="20">
+  <a:schemeClr val="dk1"/>
   <cs:variation>
-    <a:lumMod val="60000"/>
+    <a:tint val="88500"/>
   </cs:variation>
   <cs:variation>
-    <a:lumMod val="80000"/>
-    <a:lumOff val="20000"/>
+    <a:tint val="55000"/>
   </cs:variation>
   <cs:variation>
-    <a:lumMod val="80000"/>
+    <a:tint val="75000"/>
   </cs:variation>
   <cs:variation>
-    <a:lumMod val="60000"/>
-    <a:lumOff val="40000"/>
+    <a:tint val="98500"/>
   </cs:variation>
   <cs:variation>
-    <a:lumMod val="50000"/>
+    <a:tint val="30000"/>
   </cs:variation>
   <cs:variation>
-    <a:lumMod val="70000"/>
-    <a:lumOff val="30000"/>
+    <a:tint val="60000"/>
   </cs:variation>
   <cs:variation>
-    <a:lumMod val="70000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-    <a:lumOff val="50000"/>
+    <a:tint val="80000"/>
   </cs:variation>
 </cs:colorStyle>
 </file>
@@ -1602,89 +1604,14 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>9525</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>64553</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>9524</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>9525</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="5" name="Retângulo 4">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A82C4C0C-4DF7-7D14-5DD9-186959E0B1AF}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="304800" y="64553"/>
-          <a:ext cx="6143624" cy="706972"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:blipFill dpi="0" rotWithShape="1">
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
-            <a:alphaModFix amt="80000"/>
-          </a:blip>
-          <a:srcRect/>
-          <a:stretch>
-            <a:fillRect/>
-          </a:stretch>
-        </a:blipFill>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" anchor="ctr">
-          <a:noAutofit/>
-        </a:bodyPr>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="pt-BR" sz="2400" b="0" cap="none" spc="0">
-              <a:ln w="0"/>
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-              <a:effectLst>
-                <a:outerShdw blurRad="38100" dist="19050" dir="2700000" algn="tl" rotWithShape="0">
-                  <a:schemeClr val="dk1">
-                    <a:alpha val="40000"/>
-                  </a:schemeClr>
-                </a:outerShdw>
-              </a:effectLst>
-              <a:latin typeface="Baguet Script" panose="00000500000000000000" pitchFamily="2" charset="0"/>
-              <a:ea typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t>Simulador de Investimentos</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
       <xdr:colOff>11905</xdr:colOff>
-      <xdr:row>36</xdr:row>
+      <xdr:row>35</xdr:row>
       <xdr:rowOff>152399</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>11905</xdr:colOff>
-      <xdr:row>51</xdr:row>
+      <xdr:row>50</xdr:row>
       <xdr:rowOff>38099</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -1704,23 +1631,143 @@
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>35717</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>11906</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="Retângulo: Cantos Superiores Arredondados 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A61FF153-B7B4-2CCB-06FC-18202DF4AEF3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="297656" y="35717"/>
+          <a:ext cx="6155531" cy="642939"/>
+        </a:xfrm>
+        <a:prstGeom prst="round2SameRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="dk1"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="1001">
+          <a:schemeClr val="dk1"/>
+        </a:fillRef>
+        <a:effectRef idx="3">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="pt-BR" sz="2800" b="1" i="0">
+              <a:latin typeface="Century Gothic" panose="020B0502020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>Simulador de Investimentos</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1000122</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>142874</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1914522</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>152399</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="10" name="Gráfico 9" descr="Oferta e procura estrutura de tópicos">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BE8FEAE1-1C4A-5C99-C95C-3EA82E271612}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
+              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId3"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5393528" y="142874"/>
+          <a:ext cx="914400" cy="914400"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{8112ACD8-FC09-46BF-9175-6797D5B7777D}" name="Tab_Auxiliar" displayName="Tab_Auxiliar" ref="A2:D20" totalsRowShown="0" headerRowDxfId="1" dataDxfId="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{8112ACD8-FC09-46BF-9175-6797D5B7777D}" name="Tab_Auxiliar" displayName="Tab_Auxiliar" ref="A2:D20" totalsRowShown="0" headerRowDxfId="5" dataDxfId="4">
   <autoFilter ref="A2:D20" xr:uid="{8112ACD8-FC09-46BF-9175-6797D5B7777D}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{20943268-7093-471F-9A29-24432FD594AD}" name="CHAVE" dataDxfId="5"/>
-    <tableColumn id="2" xr3:uid="{01C13B99-C8A4-4680-991B-9EA7A807B4DA}" name="PERFIL" dataDxfId="4"/>
-    <tableColumn id="3" xr3:uid="{0A8F6217-9473-45C3-9480-E9EF05AE98D3}" name="TIPO DE FII" dataDxfId="3"/>
-    <tableColumn id="4" xr3:uid="{F1353A3B-ADA8-462A-8C44-AA0E7B33EA95}" name="%" dataDxfId="2" dataCellStyle="Porcentagem"/>
+    <tableColumn id="1" xr3:uid="{20943268-7093-471F-9A29-24432FD594AD}" name="CHAVE" dataDxfId="3"/>
+    <tableColumn id="2" xr3:uid="{01C13B99-C8A4-4680-991B-9EA7A807B4DA}" name="PERFIL" dataDxfId="2"/>
+    <tableColumn id="3" xr3:uid="{0A8F6217-9473-45C3-9480-E9EF05AE98D3}" name="TIPO DE FII" dataDxfId="1"/>
+    <tableColumn id="4" xr3:uid="{F1353A3B-ADA8-462A-8C44-AA0E7B33EA95}" name="%" dataDxfId="0" dataCellStyle="Porcentagem"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2043,358 +2090,352 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F9D1864F-2207-42A9-A2FD-784020E63C3E}">
-  <dimension ref="A6:E36"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A5:E35"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="18" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.42578125" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="4" width="30.7109375" customWidth="1"/>
-    <col min="5" max="5" width="5.7109375" customWidth="1"/>
-    <col min="6" max="16384" width="13.28515625" hidden="1"/>
+    <col min="1" max="1" width="4.42578125" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="4" width="30.7109375" style="7" customWidth="1"/>
+    <col min="5" max="5" width="5.7109375" style="7" customWidth="1"/>
+    <col min="6" max="16384" width="13.28515625" style="7" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="6" spans="1:4" ht="21.75" x14ac:dyDescent="0.25">
-      <c r="B6" s="12" t="s">
+    <row r="5" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B5" s="34" t="s">
         <v>0</v>
       </c>
-      <c r="C6" s="13"/>
-      <c r="D6" s="14"/>
-    </row>
-    <row r="7" spans="1:4" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="3"/>
-      <c r="B7" s="17" t="s">
+      <c r="C5" s="35"/>
+      <c r="D5" s="36"/>
+    </row>
+    <row r="6" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B6" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="C7" s="18"/>
-      <c r="D7" s="19">
+      <c r="C6" s="9"/>
+      <c r="D6" s="10">
         <v>4000</v>
       </c>
     </row>
-    <row r="8" spans="1:4" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A8" s="3"/>
-      <c r="B8" s="17" t="s">
+    <row r="7" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B7" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="C8" s="18"/>
-      <c r="D8" s="20">
+      <c r="C7" s="9"/>
+      <c r="D7" s="11">
         <v>6.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="9" spans="1:4" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A9" s="3"/>
-      <c r="B9" s="17" t="s">
-        <v>5</v>
-      </c>
-      <c r="C9" s="18"/>
-      <c r="D9" s="21">
+    <row r="8" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B8" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C8" s="9"/>
+      <c r="D8" s="12">
         <v>0.2</v>
       </c>
     </row>
-    <row r="10" spans="1:4" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A10" s="3"/>
-      <c r="B10" s="22" t="s">
+    <row r="9" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B9" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="C10" s="23"/>
-      <c r="D10" s="24">
-        <f>IF($D$7="","",$D$7*$D$9)</f>
+      <c r="C9" s="14"/>
+      <c r="D9" s="15">
+        <f>IF($D$6="","",$D$6*$D$8)</f>
         <v>800</v>
       </c>
     </row>
-    <row r="12" spans="1:4" s="16" customFormat="1" ht="21.75" x14ac:dyDescent="0.35">
-      <c r="A12" s="15"/>
-      <c r="B12" s="12" t="s">
-        <v>4</v>
-      </c>
-      <c r="C12" s="13"/>
-      <c r="D12" s="14"/>
-    </row>
-    <row r="13" spans="1:4" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A13" s="3"/>
-      <c r="B13" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="C13" s="18"/>
-      <c r="D13" s="25">
+    <row r="10" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B10" s="31"/>
+      <c r="C10" s="31"/>
+      <c r="D10" s="31"/>
+    </row>
+    <row r="11" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B11" s="34" t="s">
+        <v>54</v>
+      </c>
+      <c r="C11" s="35"/>
+      <c r="D11" s="36"/>
+    </row>
+    <row r="12" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B12" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C12" s="9"/>
+      <c r="D12" s="16">
         <f>Valor</f>
         <v>800</v>
       </c>
     </row>
-    <row r="14" spans="1:4" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A14" s="3"/>
-      <c r="B14" s="17" t="s">
+    <row r="13" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B13" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C13" s="9"/>
+      <c r="D13" s="17">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B14" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="C14" s="18"/>
-      <c r="D14" s="26">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A15" s="3"/>
-      <c r="B15" s="17" t="s">
-        <v>15</v>
-      </c>
-      <c r="C15" s="18"/>
-      <c r="D15" s="20">
+      <c r="C14" s="9"/>
+      <c r="D14" s="11">
         <v>1.04E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:4" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A16" s="3"/>
-      <c r="B16" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="C16" s="18"/>
-      <c r="D16" s="25">
+    <row r="15" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B15" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15" s="9"/>
+      <c r="D15" s="16">
         <f>FV(Taxa_Mensal,Qtde_Anos*12,Aporte*-1)</f>
         <v>21681.426163999589</v>
       </c>
     </row>
-    <row r="17" spans="1:4" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A17" s="3"/>
-      <c r="B17" s="22" t="s">
-        <v>18</v>
-      </c>
-      <c r="C17" s="23"/>
-      <c r="D17" s="24">
+    <row r="16" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B16" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="C16" s="14"/>
+      <c r="D16" s="15">
         <f>Patrimonio*Rendimento</f>
         <v>130.08855698399753</v>
       </c>
     </row>
-    <row r="19" spans="1:4" s="31" customFormat="1" ht="21.75" x14ac:dyDescent="0.25">
-      <c r="A19" s="27"/>
-      <c r="B19" s="28" t="s">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B17" s="31"/>
+      <c r="C17" s="31"/>
+      <c r="D17" s="31"/>
+    </row>
+    <row r="18" spans="1:4" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="18"/>
+      <c r="B18" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" s="21" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="3">
+        <v>2</v>
+      </c>
+      <c r="B19" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="C19" s="29" t="s">
+      <c r="C19" s="20">
+        <f>FV(Taxa_Mensal,$A19*12,Aporte*-1)</f>
+        <v>21681.426163999589</v>
+      </c>
+      <c r="D19" s="16">
+        <f>$C19*Rendimento</f>
+        <v>130.08855698399753</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" s="21" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="3">
+        <v>5</v>
+      </c>
+      <c r="B20" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C20" s="20">
+        <f>FV(Taxa_Mensal,$A20*12,Aporte*-1)</f>
+        <v>66182.612589424534</v>
+      </c>
+      <c r="D20" s="16">
+        <f>$C20*Rendimento</f>
+        <v>397.09567553654722</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" s="21" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="3">
+        <v>10</v>
+      </c>
+      <c r="B21" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="20">
+        <f>FV(Taxa_Mensal,$A21*12,Aporte*-1)</f>
+        <v>189307.02189795321</v>
+      </c>
+      <c r="D21" s="16">
+        <f>$C21*Rendimento</f>
+        <v>1135.8421313877193</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" s="21" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="3">
+        <v>20</v>
+      </c>
+      <c r="B22" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C22" s="20">
+        <f>FV(Taxa_Mensal,$A22*12,Aporte*-1)</f>
+        <v>844496.97481424408</v>
+      </c>
+      <c r="D22" s="16">
+        <f>$C22*Rendimento</f>
+        <v>5066.9818488854644</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" s="21" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="3">
+        <v>30</v>
+      </c>
+      <c r="B23" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C23" s="22">
+        <f>FV(Taxa_Mensal,$A23*12,Aporte*-1)</f>
+        <v>3112103.6916630967</v>
+      </c>
+      <c r="D23" s="15">
+        <f>$C23*Rendimento</f>
+        <v>18672.622149978579</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" s="21" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="3"/>
+      <c r="B24" s="23"/>
+      <c r="C24" s="24"/>
+      <c r="D24" s="25"/>
+    </row>
+    <row r="25" spans="1:4" s="21" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="3"/>
+      <c r="B25" s="32" t="s">
+        <v>12</v>
+      </c>
+      <c r="C25" s="33"/>
+      <c r="D25" s="26" t="s">
         <v>19</v>
       </c>
-      <c r="D19" s="30" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A20" s="3">
-        <v>2</v>
-      </c>
-      <c r="B20" s="17" t="s">
-        <v>7</v>
-      </c>
-      <c r="C20" s="32">
-        <f>FV(Taxa_Mensal,$A20*12,Aporte*-1)</f>
-        <v>21681.426163999589</v>
-      </c>
-      <c r="D20" s="25">
-        <f>$C20*Rendimento</f>
-        <v>130.08855698399753</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A21" s="3">
-        <v>5</v>
-      </c>
-      <c r="B21" s="17" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="32">
-        <f>FV(Taxa_Mensal,$A21*12,Aporte*-1)</f>
-        <v>66182.612589424534</v>
-      </c>
-      <c r="D21" s="25">
-        <f>$C21*Rendimento</f>
-        <v>397.09567553654722</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A22" s="3">
-        <v>10</v>
-      </c>
-      <c r="B22" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="C22" s="32">
-        <f>FV(Taxa_Mensal,$A22*12,Aporte*-1)</f>
-        <v>189307.02189795321</v>
-      </c>
-      <c r="D22" s="25">
-        <f>$C22*Rendimento</f>
-        <v>1135.8421313877193</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A23" s="3">
-        <v>20</v>
-      </c>
-      <c r="B23" s="17" t="s">
-        <v>10</v>
-      </c>
-      <c r="C23" s="32">
-        <f>FV(Taxa_Mensal,$A23*12,Aporte*-1)</f>
-        <v>844496.97481424408</v>
-      </c>
-      <c r="D23" s="25">
-        <f>$C23*Rendimento</f>
-        <v>5066.9818488854644</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A24" s="3">
-        <v>30</v>
-      </c>
-      <c r="B24" s="22" t="s">
-        <v>11</v>
-      </c>
-      <c r="C24" s="33">
-        <f>FV(Taxa_Mensal,$A24*12,Aporte*-1)</f>
-        <v>3112103.6916630967</v>
-      </c>
-      <c r="D24" s="24">
-        <f>$C24*Rendimento</f>
-        <v>18672.622149978579</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A25" s="3"/>
-      <c r="B25" s="36"/>
-      <c r="C25" s="37"/>
-      <c r="D25" s="38"/>
-    </row>
-    <row r="26" spans="1:4" s="4" customFormat="1" ht="21.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="26" spans="1:4" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="3"/>
-      <c r="B26" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="C26" s="9"/>
-      <c r="D26" s="10" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" s="4" customFormat="1" ht="21.75" x14ac:dyDescent="0.25">
-      <c r="A27" s="3"/>
-      <c r="B27" s="8" t="s">
+      <c r="B26" s="32" t="s">
         <v>3</v>
       </c>
-      <c r="C27" s="9"/>
-      <c r="D27" s="11">
+      <c r="C26" s="33"/>
+      <c r="D26" s="27">
         <f>Aporte</f>
         <v>800</v>
       </c>
     </row>
-    <row r="29" spans="1:4" s="31" customFormat="1" ht="21.75" x14ac:dyDescent="0.25">
-      <c r="A29" s="27"/>
-      <c r="B29" s="28" t="s">
-        <v>54</v>
-      </c>
-      <c r="C29" s="29" t="s">
+    <row r="28" spans="1:4" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="18"/>
+      <c r="B28" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="D28" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="D29" s="30" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A30" s="3"/>
-      <c r="B30" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="C30" s="34">
-        <f>VLOOKUP($D$26&amp;"-"&amp;$B30,Auxiliar!$A:$D,4,FALSE)</f>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B29" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C29" s="28">
+        <f>VLOOKUP($D$25&amp;"-"&amp;$B29,Auxiliar!$A:$D,4,FALSE)</f>
+        <v>0.3</v>
+      </c>
+      <c r="D29" s="16">
+        <f t="shared" ref="D29:D34" si="0">C29*$D$26</f>
+        <v>240</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B30" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C30" s="28">
+        <f>VLOOKUP($D$25&amp;"-"&amp;$B30,Auxiliar!$A:$D,4,FALSE)</f>
         <v>0.5</v>
       </c>
-      <c r="D30" s="25">
-        <f>C30*$D$27</f>
+      <c r="D30" s="16">
+        <f t="shared" si="0"/>
         <v>400</v>
       </c>
     </row>
-    <row r="31" spans="1:4" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A31" s="3"/>
-      <c r="B31" s="17" t="s">
-        <v>28</v>
-      </c>
-      <c r="C31" s="34">
-        <f>VLOOKUP($D$26&amp;"-"&amp;$B31,Auxiliar!$A:$D,4,FALSE)</f>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B31" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="C31" s="28">
+        <f>VLOOKUP($D$25&amp;"-"&amp;$B31,Auxiliar!$A:$D,4,FALSE)</f>
         <v>0.1</v>
       </c>
-      <c r="D31" s="25">
-        <f>C31*$D$27</f>
+      <c r="D31" s="16">
+        <f t="shared" si="0"/>
         <v>80</v>
       </c>
     </row>
-    <row r="32" spans="1:4" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A32" s="3"/>
-      <c r="B32" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="C32" s="34">
-        <f>VLOOKUP($D$26&amp;"-"&amp;$B32,Auxiliar!$A:$D,4,FALSE)</f>
-        <v>0.05</v>
-      </c>
-      <c r="D32" s="25">
-        <f>C32*$D$27</f>
-        <v>40</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A33" s="3"/>
-      <c r="B33" s="17" t="s">
-        <v>32</v>
-      </c>
-      <c r="C33" s="34">
-        <f>VLOOKUP($D$26&amp;"-"&amp;$B33,Auxiliar!$A:$D,4,FALSE)</f>
-        <v>0.05</v>
-      </c>
-      <c r="D33" s="25">
-        <f>C33*$D$27</f>
-        <v>40</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A34" s="3"/>
-      <c r="B34" s="17" t="s">
-        <v>34</v>
-      </c>
-      <c r="C34" s="34">
-        <f>VLOOKUP($D$26&amp;"-"&amp;$B34,Auxiliar!$A:$D,4,FALSE)</f>
-        <v>0.2</v>
-      </c>
-      <c r="D34" s="25">
-        <f>C34*$D$27</f>
-        <v>160</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A35" s="3"/>
-      <c r="B35" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="C35" s="34">
-        <f>VLOOKUP($D$26&amp;"-"&amp;$B35,Auxiliar!$A:$D,4,FALSE)</f>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B32" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="C32" s="28">
+        <f>VLOOKUP($D$25&amp;"-"&amp;$B32,Auxiliar!$A:$D,4,FALSE)</f>
         <v>0.1</v>
       </c>
-      <c r="D35" s="25">
-        <f>C35*$D$27</f>
+      <c r="D32" s="16">
+        <f t="shared" si="0"/>
         <v>80</v>
       </c>
     </row>
-    <row r="36" spans="1:4" ht="21.75" x14ac:dyDescent="0.25">
-      <c r="B36" s="28" t="s">
-        <v>53</v>
-      </c>
-      <c r="C36" s="7"/>
-      <c r="D36" s="35">
-        <f>SUM(D30:D35)</f>
+    <row r="33" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B33" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="C33" s="28">
+        <f>VLOOKUP($D$25&amp;"-"&amp;$B33,Auxiliar!$A:$D,4,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="D33" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B34" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="C34" s="28">
+        <f>VLOOKUP($D$25&amp;"-"&amp;$B34,Auxiliar!$A:$D,4,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="D34" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B35" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C35" s="29"/>
+      <c r="D35" s="30">
+        <f>SUM(D29:D34)</f>
         <v>800</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="B27:C27"/>
     <mergeCell ref="B26:C26"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="B12:D12"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B11:D11"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D26" xr:uid="{92379BF6-4ADF-4710-811D-A68D1BAF655E}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D25" xr:uid="{92379BF6-4ADF-4710-811D-A68D1BAF655E}">
       <formula1>"Conservador,Moderado,Ousado"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2408,276 +2449,276 @@
   <dimension ref="A2:D20"/>
   <sheetFormatPr defaultColWidth="30.7109375" defaultRowHeight="12.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="33.5703125" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.5703125" style="5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="21.140625" style="5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.5703125" style="6" bestFit="1" customWidth="1"/>
-    <col min="5" max="16384" width="30.7109375" style="5"/>
+    <col min="1" max="1" width="33.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="16384" width="30.7109375" style="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="C2" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="D2" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="D2" s="6" t="s">
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
+      <c r="B3" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B3" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C3" s="5" t="s">
+      <c r="D3" s="2">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="D3" s="6">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
+      <c r="B4" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B4" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C4" s="5" t="s">
+      <c r="D4" s="2">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D4" s="6">
+      <c r="B5" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D5" s="2">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D6" s="2">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D7" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D8" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D9" s="2">
+        <v>0.32</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D10" s="2">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D11" s="2">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D12" s="2">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D13" s="2">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D14" s="2">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D15" s="2">
         <v>0.5</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D16" s="2">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C17" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B5" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="D5" s="6">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
+      <c r="D17" s="2">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C18" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B6" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="D6" s="6">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="5" t="s">
+      <c r="D18" s="2">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C19" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B7" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="D7" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="5" t="s">
+      <c r="D19" s="2">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C20" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B8" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="D8" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="D9" s="6">
-        <v>0.32</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="D10" s="6">
-        <v>0.35</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="D11" s="6">
-        <v>0.08</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="D12" s="6">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="D13" s="6">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="D14" s="6">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="D15" s="6">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="D16" s="6">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="D17" s="6">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="D18" s="6">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="D19" s="6">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="D20" s="6">
+      <c r="D20" s="2">
         <v>0.1</v>
       </c>
     </row>

--- a/App_Investimentos.xlsx
+++ b/App_Investimentos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/217cc67307c45ea1/Área de Trabalho/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="93" documentId="13_ncr:1_{AA77CDAA-366C-4305-9366-5619397C2ED5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8142D5CE-75E9-406F-8756-0A29E0C3EAE5}"/>
+  <xr:revisionPtr revIDLastSave="99" documentId="13_ncr:1_{AA77CDAA-366C-4305-9366-5619397C2ED5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4935ADB3-3074-4C1A-9E90-43A947758742}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" tabRatio="0" xr2:uid="{5D7F3A9A-47AD-4D1B-B95A-5B68640EB23A}"/>
   </bookViews>
@@ -602,10 +602,10 @@
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="101"/>
+      <c14:style val="102"/>
     </mc:Choice>
     <mc:Fallback>
-      <c:style val="1"/>
+      <c:style val="2"/>
     </mc:Fallback>
   </mc:AlternateContent>
   <c:chart>
@@ -635,16 +635,13 @@
               <a:gradFill>
                 <a:gsLst>
                   <a:gs pos="100000">
-                    <a:schemeClr val="dk1">
-                      <a:tint val="88500"/>
+                    <a:schemeClr val="accent2">
                       <a:lumMod val="60000"/>
                       <a:lumOff val="40000"/>
                     </a:schemeClr>
                   </a:gs>
                   <a:gs pos="0">
-                    <a:schemeClr val="dk1">
-                      <a:tint val="88500"/>
-                    </a:schemeClr>
+                    <a:schemeClr val="accent2"/>
                   </a:gs>
                 </a:gsLst>
                 <a:lin ang="5400000" scaled="0"/>
@@ -669,16 +666,13 @@
               <a:gradFill>
                 <a:gsLst>
                   <a:gs pos="100000">
-                    <a:schemeClr val="dk1">
-                      <a:tint val="55000"/>
+                    <a:schemeClr val="accent4">
                       <a:lumMod val="60000"/>
                       <a:lumOff val="40000"/>
                     </a:schemeClr>
                   </a:gs>
                   <a:gs pos="0">
-                    <a:schemeClr val="dk1">
-                      <a:tint val="55000"/>
-                    </a:schemeClr>
+                    <a:schemeClr val="accent4"/>
                   </a:gs>
                 </a:gsLst>
                 <a:lin ang="5400000" scaled="0"/>
@@ -703,16 +697,13 @@
               <a:gradFill>
                 <a:gsLst>
                   <a:gs pos="100000">
-                    <a:schemeClr val="dk1">
-                      <a:tint val="75000"/>
+                    <a:schemeClr val="accent6">
                       <a:lumMod val="60000"/>
                       <a:lumOff val="40000"/>
                     </a:schemeClr>
                   </a:gs>
                   <a:gs pos="0">
-                    <a:schemeClr val="dk1">
-                      <a:tint val="75000"/>
-                    </a:schemeClr>
+                    <a:schemeClr val="accent6"/>
                   </a:gs>
                 </a:gsLst>
                 <a:lin ang="5400000" scaled="0"/>
@@ -737,15 +728,15 @@
               <a:gradFill>
                 <a:gsLst>
                   <a:gs pos="100000">
-                    <a:schemeClr val="dk1">
-                      <a:tint val="98500"/>
+                    <a:schemeClr val="accent2">
+                      <a:lumMod val="60000"/>
                       <a:lumMod val="60000"/>
                       <a:lumOff val="40000"/>
                     </a:schemeClr>
                   </a:gs>
                   <a:gs pos="0">
-                    <a:schemeClr val="dk1">
-                      <a:tint val="98500"/>
+                    <a:schemeClr val="accent2">
+                      <a:lumMod val="60000"/>
                     </a:schemeClr>
                   </a:gs>
                 </a:gsLst>
@@ -771,15 +762,15 @@
               <a:gradFill>
                 <a:gsLst>
                   <a:gs pos="100000">
-                    <a:schemeClr val="dk1">
-                      <a:tint val="30000"/>
+                    <a:schemeClr val="accent4">
+                      <a:lumMod val="60000"/>
                       <a:lumMod val="60000"/>
                       <a:lumOff val="40000"/>
                     </a:schemeClr>
                   </a:gs>
                   <a:gs pos="0">
-                    <a:schemeClr val="dk1">
-                      <a:tint val="30000"/>
+                    <a:schemeClr val="accent4">
+                      <a:lumMod val="60000"/>
                     </a:schemeClr>
                   </a:gs>
                 </a:gsLst>
@@ -805,15 +796,15 @@
               <a:gradFill>
                 <a:gsLst>
                   <a:gs pos="100000">
-                    <a:schemeClr val="dk1">
-                      <a:tint val="60000"/>
+                    <a:schemeClr val="accent6">
+                      <a:lumMod val="60000"/>
                       <a:lumMod val="60000"/>
                       <a:lumOff val="40000"/>
                     </a:schemeClr>
                   </a:gs>
                   <a:gs pos="0">
-                    <a:schemeClr val="dk1">
-                      <a:tint val="60000"/>
+                    <a:schemeClr val="accent6">
+                      <a:lumMod val="60000"/>
                     </a:schemeClr>
                   </a:gs>
                 </a:gsLst>
@@ -918,22 +909,22 @@
                 <c:formatCode>0.00%</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>0.3</c:v>
+                  <c:v>0.5</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.5</c:v>
+                  <c:v>0.1</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.1</c:v>
+                  <c:v>0.05</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.1</c:v>
+                  <c:v>0.05</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0</c:v>
+                  <c:v>0.2</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0</c:v>
+                  <c:v>0.1</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1030,28 +1021,38 @@
 </file>
 
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="20">
-  <a:schemeClr val="dk1"/>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="12">
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
   <cs:variation>
-    <a:tint val="88500"/>
+    <a:lumMod val="60000"/>
   </cs:variation>
   <cs:variation>
-    <a:tint val="55000"/>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
   </cs:variation>
   <cs:variation>
-    <a:tint val="75000"/>
+    <a:lumMod val="80000"/>
   </cs:variation>
   <cs:variation>
-    <a:tint val="98500"/>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
   </cs:variation>
   <cs:variation>
-    <a:tint val="30000"/>
+    <a:lumMod val="50000"/>
   </cs:variation>
   <cs:variation>
-    <a:tint val="60000"/>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
   </cs:variation>
   <cs:variation>
-    <a:tint val="80000"/>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
   </cs:variation>
 </cs:colorStyle>
 </file>
@@ -2090,8 +2091,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F9D1864F-2207-42A9-A2FD-784020E63C3E}">
-  <dimension ref="A5:E35"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="18" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:E50"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="18" zeroHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.42578125" style="3" bestFit="1" customWidth="1"/>
     <col min="2" max="4" width="30.7109375" style="7" customWidth="1"/>
@@ -2099,6 +2100,10 @@
     <col min="6" max="16384" width="13.28515625" style="7" hidden="1"/>
   </cols>
   <sheetData>
+    <row r="1" spans="2:4" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="2:4" x14ac:dyDescent="0.25"/>
+    <row r="3" spans="2:4" x14ac:dyDescent="0.25"/>
+    <row r="4" spans="2:4" x14ac:dyDescent="0.25"/>
     <row r="5" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B5" s="34" t="s">
         <v>0</v>
@@ -2313,7 +2318,7 @@
       </c>
       <c r="C25" s="33"/>
       <c r="D25" s="26" t="s">
-        <v>19</v>
+        <v>45</v>
       </c>
     </row>
     <row r="26" spans="1:4" s="21" customFormat="1" x14ac:dyDescent="0.25">
@@ -2327,6 +2332,7 @@
         <v>800</v>
       </c>
     </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25"/>
     <row r="28" spans="1:4" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="18"/>
       <c r="B28" s="4" t="s">
@@ -2345,11 +2351,11 @@
       </c>
       <c r="C29" s="28">
         <f>VLOOKUP($D$25&amp;"-"&amp;$B29,Auxiliar!$A:$D,4,FALSE)</f>
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="D29" s="16">
         <f t="shared" ref="D29:D34" si="0">C29*$D$26</f>
-        <v>240</v>
+        <v>400</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -2358,11 +2364,11 @@
       </c>
       <c r="C30" s="28">
         <f>VLOOKUP($D$25&amp;"-"&amp;$B30,Auxiliar!$A:$D,4,FALSE)</f>
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="D30" s="16">
         <f t="shared" si="0"/>
-        <v>400</v>
+        <v>80</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -2371,11 +2377,11 @@
       </c>
       <c r="C31" s="28">
         <f>VLOOKUP($D$25&amp;"-"&amp;$B31,Auxiliar!$A:$D,4,FALSE)</f>
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="D31" s="16">
         <f t="shared" si="0"/>
-        <v>80</v>
+        <v>40</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -2384,11 +2390,11 @@
       </c>
       <c r="C32" s="28">
         <f>VLOOKUP($D$25&amp;"-"&amp;$B32,Auxiliar!$A:$D,4,FALSE)</f>
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="D32" s="16">
         <f t="shared" si="0"/>
-        <v>80</v>
+        <v>40</v>
       </c>
     </row>
     <row r="33" spans="2:4" x14ac:dyDescent="0.25">
@@ -2397,11 +2403,11 @@
       </c>
       <c r="C33" s="28">
         <f>VLOOKUP($D$25&amp;"-"&amp;$B33,Auxiliar!$A:$D,4,FALSE)</f>
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="D33" s="16">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>160</v>
       </c>
     </row>
     <row r="34" spans="2:4" x14ac:dyDescent="0.25">
@@ -2410,11 +2416,11 @@
       </c>
       <c r="C34" s="28">
         <f>VLOOKUP($D$25&amp;"-"&amp;$B34,Auxiliar!$A:$D,4,FALSE)</f>
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="D34" s="16">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>80</v>
       </c>
     </row>
     <row r="35" spans="2:4" x14ac:dyDescent="0.25">
@@ -2427,6 +2433,21 @@
         <v>800</v>
       </c>
     </row>
+    <row r="36" spans="2:4" x14ac:dyDescent="0.25"/>
+    <row r="37" spans="2:4" x14ac:dyDescent="0.25"/>
+    <row r="38" spans="2:4" x14ac:dyDescent="0.25"/>
+    <row r="39" spans="2:4" x14ac:dyDescent="0.25"/>
+    <row r="40" spans="2:4" x14ac:dyDescent="0.25"/>
+    <row r="41" spans="2:4" x14ac:dyDescent="0.25"/>
+    <row r="42" spans="2:4" x14ac:dyDescent="0.25"/>
+    <row r="43" spans="2:4" x14ac:dyDescent="0.25"/>
+    <row r="44" spans="2:4" x14ac:dyDescent="0.25"/>
+    <row r="45" spans="2:4" x14ac:dyDescent="0.25"/>
+    <row r="46" spans="2:4" x14ac:dyDescent="0.25"/>
+    <row r="47" spans="2:4" x14ac:dyDescent="0.25"/>
+    <row r="48" spans="2:4" x14ac:dyDescent="0.25"/>
+    <row r="49" x14ac:dyDescent="0.25"/>
+    <row r="50" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="B26:C26"/>
